--- a/data/ancestries.xlsx
+++ b/data/ancestries.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Human" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Human Lore" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Lore" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,7 +464,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Vigor</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>25 ft</t>
+          <t>6 ft</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Medium • 8 HP • 25 ft • bonus to Aid</t>
+          <t>Medium • Vigor 8 • 6 ft • bonus to Aid</t>
         </is>
       </c>
     </row>
@@ -636,8 +636,8 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Short lives teach humans to close ranks and pull together.</t>
@@ -645,11 +645,11 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You gain a +1 status bonus on checks to Aid. If you are Expert in Human, this becomes a +2 status bonus. If you are Master, +3. If you are Legendary, +4.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>You gain a +1 Condition bonus on checks to Aid. If you are Expert in Human, this becomes a +2 Condition bonus. If you are Master, +3. If you are Legendary, +4.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -662,13 +662,13 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Humanity</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>You were raised to reach, and you have not stopped reaching since.</t>
@@ -679,7 +679,7 @@
           <t>You gain a Calling Talent Point.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>1 in any Calling</t>
@@ -697,13 +697,13 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Humanity</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Your adaptability shows in how fast you pick up useful skills.</t>
@@ -714,7 +714,7 @@
           <t>You gain a Skill Talent Point.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1 in any Skill</t>
@@ -732,21 +732,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Humanity</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>The first time each encounter you would be knocked prone, you are not.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -759,21 +759,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Humanity</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>While an ally is adjacent to you, both of you gain a +1 circumstance bonus to Guard for physical Attacks.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>While an ally is adjacent to you, both of you gain a +1 Situation bonus to Guard for physical Attacks.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -791,8 +791,8 @@
           <t>h</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Some humans refuse to be one thing; you are a whole toolbox wearing boots.</t>
@@ -825,13 +825,13 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Versatile Human</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>You have done a little of everything, and it shows.</t>
@@ -839,7 +839,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>You gain a +1 circumstance bonus to your Untrained checks.</t>
+          <t>You gain a +1 Situation bonus to your Untrained checks.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
           <t>Wits</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -865,8 +865,8 @@
           <t>h</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Some humans carry the light everyone else steers by.</t>
@@ -874,16 +874,16 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Allies within 15 feet gain a +1 circumstance bonus to their first Defense roll each round while they can see or hear you.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t>Allies within 15 feet gain a +1 Situation bonus to their first Defense roll each round while they can see or hear you.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Steady the Line ↺</t>
+          <t>Steady the Line ❶↺</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -891,13 +891,13 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Torchbearer Human</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your voice finds the one who is faltering.</t>
@@ -905,12 +905,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Trigger An adjacent ally is Grazed.
-Effect No zone of theirs becomes Exposed. Once per round.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> An adjacent ally's Strike is Stopped and would Expose them.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Effect</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> It Exposes nothing.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1096,7 +1117,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Hit Points</t>
+          <t>Vigor</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1125,7 +1146,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25 ft</t>
+          <t>6 ft</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1182,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Some humans carry the light everyone else steers by. You gain a +2 circumstance bonus to checks to rally, reassure, or embolden others, rising to +3 at Expert rank, +4 at Master, and +5 at Legendary. Allies within 15 feet gain a +1 circumstance bonus to saves against fear while they can see or hear you, and that reach grows to 30 feet at Master.</t>
+          <t>Some humans carry the light everyone else steers by. You gain a +2 Situation bonus to checks to rally, reassure, or embolden others, rising to +3 at Expert rank, +4 at Master, and +5 at Legendary. Allies within 15 feet gain a +1 Situation bonus to saves against fear while they can see or hear you, and that reach grows to 30 feet at Master.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1194,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Some humans refuse to be one thing; you are a whole toolbox wearing boots. You gain 1 talent point to use to open any non-Skill constellation (the point buys its root). Breadth is its own talent: checks in any constellation where you have bought exactly one talent gain a +1 circumstance bonus, rising to +2 at Expert rank, +3 at Master, and +4 at Legendary.</t>
+          <t>Some humans refuse to be one thing; you are a whole toolbox wearing boots. You gain 1 talent point to use to open any non-Skill constellation (the point buys its root). Breadth is its own talent: checks in any constellation where you have bought exactly one talent gain a +1 Situation bonus, rising to +2 at Expert rank, +3 at Master, and +4 at Legendary.</t>
         </is>
       </c>
     </row>
